--- a/docs/alliance-templates/alliance-projects.xlsx
+++ b/docs/alliance-templates/alliance-projects.xlsx
@@ -7,27 +7,19 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="合作项目" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'合作项目'!$A$2:$F$2</definedName>
+    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'Sheet1'!$A$1:$F$6</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>填写说明：
-* 必填列。
-项目类型：文本，选填
-项目阶段：initiation（启动） / execution（执行） / acceptance（验收） / closure（关闭），默认为 initiation
-开始日期 / 结束日期：格式 YYYY-MM-DD，选填
-描述：文本，选填</t>
-  </si>
-  <si>
-    <t>项目名称 *</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+  <si>
+    <t>项目名称</t>
   </si>
   <si>
     <t>项目类型</t>
@@ -43,13 +35,88 @@
   </si>
   <si>
     <t>描述</t>
+  </si>
+  <si>
+    <t>人工智能联合实验室</t>
+  </si>
+  <si>
+    <t>技术研发</t>
+  </si>
+  <si>
+    <t>execution</t>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+  </si>
+  <si>
+    <t>2027-02-28</t>
+  </si>
+  <si>
+    <t>联合开展人工智能算法研究与人才培养项目</t>
+  </si>
+  <si>
+    <t>智能制造实训基地</t>
+  </si>
+  <si>
+    <t>实训基地</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>2026-12-31</t>
+  </si>
+  <si>
+    <t>建设智能制造产线实训基地，提供学生实习实训</t>
+  </si>
+  <si>
+    <t>大数据分析课程共建</t>
+  </si>
+  <si>
+    <t>课程共建</t>
+  </si>
+  <si>
+    <t>initiation</t>
+  </si>
+  <si>
+    <t>2026-06-01</t>
+  </si>
+  <si>
+    <t>校企联合开发大数据分析方向课程资源</t>
+  </si>
+  <si>
+    <t>新能源技术研究中心</t>
+  </si>
+  <si>
+    <t>2025-09-01</t>
+  </si>
+  <si>
+    <t>2028-08-31</t>
+  </si>
+  <si>
+    <t>围绕新能源汽车电池技术开展联合攻关</t>
+  </si>
+  <si>
+    <t>数字营销实战项目</t>
+  </si>
+  <si>
+    <t>创新创业</t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-10-31</t>
+  </si>
+  <si>
+    <t>学生参与企业真实数字营销项目实践</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,14 +126,8 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color/>
       <sz val="11"/>
-    </font>
-    <font>
-      <family val="2"/>
-      <i val="1"/>
-      <color rgb="FF808080"/>
-      <sz val="10"/>
     </font>
   </fonts>
   <fills count="3">
@@ -78,7 +139,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4472C4"/>
+        <fgColor rgb="FFCCE5FF"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,34 +151,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFD9D9D9"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9D9D9"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9D9D9"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9D9D9"/>
-      </bottom>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center" wrapText="true"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
-      <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -384,52 +429,139 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetPr filterMode="true"/>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="28"/>
-    <col customWidth="true" max="2" min="2" width="20"/>
-    <col customWidth="true" max="3" min="3" width="22"/>
-    <col customWidth="true" max="5" min="4" width="16"/>
-    <col customWidth="true" max="6" min="6" width="48"/>
+    <col customWidth="true" max="2" min="2" width="16"/>
+    <col customWidth="true" max="5" min="3" width="14"/>
+    <col customWidth="true" max="6" min="6" width="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="112" customHeight="true">
-      <c r="A1" s="3" t="s">
+    <row r="1" ht="24" customHeight="true">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" ht="28" customHeight="true">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
+    <row r="2" ht="20" customHeight="true">
+      <c r="A2" s="2" t="s">
         <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="true">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="true">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="true">
+      <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="true">
+      <c r="A6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$2:$F$2"/>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
+  <autoFilter ref="$A$1:$F$6"/>
 </worksheet>
 </file>
--- a/docs/alliance-templates/alliance-projects.xlsx
+++ b/docs/alliance-templates/alliance-projects.xlsx
@@ -1,122 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="true" defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合作项目" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="true" localSheetId="0" name="_xlnm._FilterDatabase">'Sheet1'!$A$1:$F$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'合作项目'!$A$2:$F$2</definedName>
   </definedNames>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="122211" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
-  <si>
-    <t>项目名称</t>
-  </si>
-  <si>
-    <t>项目类型</t>
-  </si>
-  <si>
-    <t>项目阶段</t>
-  </si>
-  <si>
-    <t>开始日期</t>
-  </si>
-  <si>
-    <t>结束日期</t>
-  </si>
-  <si>
-    <t>描述</t>
-  </si>
-  <si>
-    <t>人工智能联合实验室</t>
-  </si>
-  <si>
-    <t>技术研发</t>
-  </si>
-  <si>
-    <t>execution</t>
-  </si>
-  <si>
-    <t>2026-03-01</t>
-  </si>
-  <si>
-    <t>2027-02-28</t>
-  </si>
-  <si>
-    <t>联合开展人工智能算法研究与人才培养项目</t>
-  </si>
-  <si>
-    <t>智能制造实训基地</t>
-  </si>
-  <si>
-    <t>实训基地</t>
-  </si>
-  <si>
-    <t>2026-01-15</t>
-  </si>
-  <si>
-    <t>2026-12-31</t>
-  </si>
-  <si>
-    <t>建设智能制造产线实训基地，提供学生实习实训</t>
-  </si>
-  <si>
-    <t>大数据分析课程共建</t>
-  </si>
-  <si>
-    <t>课程共建</t>
-  </si>
-  <si>
-    <t>initiation</t>
-  </si>
-  <si>
-    <t>2026-06-01</t>
-  </si>
-  <si>
-    <t>校企联合开发大数据分析方向课程资源</t>
-  </si>
-  <si>
-    <t>新能源技术研究中心</t>
-  </si>
-  <si>
-    <t>2025-09-01</t>
-  </si>
-  <si>
-    <t>2028-08-31</t>
-  </si>
-  <si>
-    <t>围绕新能源汽车电池技术开展联合攻关</t>
-  </si>
-  <si>
-    <t>数字营销实战项目</t>
-  </si>
-  <si>
-    <t>创新创业</t>
-  </si>
-  <si>
-    <t>2026-04-01</t>
-  </si>
-  <si>
-    <t>2026-10-31</t>
-  </si>
-  <si>
-    <t>学生参与企业真实数字营销项目实践</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -126,13 +28,23 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -142,8 +54,20 @@
         <fgColor rgb="FFCCE5FF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -152,24 +76,113 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="00B0B0B0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="false">
-      <alignment/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -430,138 +443,236 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr filterMode="true"/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="28"/>
-    <col customWidth="true" max="2" min="2" width="16"/>
-    <col customWidth="true" max="5" min="3" width="14"/>
-    <col customWidth="true" max="6" min="6" width="40"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="true">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
+    <row r="1" ht="128" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>填写说明：
+* 必填列。
+项目类型：文本，选填
+项目阶段：initiation（启动） / execution（执行） / acceptance（验收） / closure（关闭），默认为 initiation
+开始日期 / 结束日期：格式 YYYY-MM-DD，选填
+描述：文本，选填</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="n"/>
+      <c r="C1" s="4" t="n"/>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
     </row>
-    <row r="2" ht="20" customHeight="true">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>11</v>
+    <row r="2" ht="28" customHeight="1">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>项目名称 *</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>项目类型</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>项目阶段</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>开始日期</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>结束日期</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="true">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>16</v>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>人工智能联合实验室</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>技术研发</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>execution</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>2027-02-28</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>联合开展人工智能算法研究与人才培养项目</t>
+        </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="true">
-      <c r="A4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>21</v>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>智能制造实训基地</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>实训基地</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>execution</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-15</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>建设智能制造产线实训基地，提供学生实习实训</t>
+        </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="true">
-      <c r="A5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>25</v>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>大数据分析课程共建</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>课程共建</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>initiation</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>校企联合开发大数据分析方向课程资源</t>
+        </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="true">
-      <c r="A6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>30</v>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>新能源技术研究中心</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>技术研发</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>execution</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>2028-08-31</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>围绕新能源汽车电池技术开展联合攻关</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>数字营销实战项目</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>创新创业</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>initiation</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>学生参与企业真实数字营销项目实践</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$F$6"/>
+  <autoFilter ref="A2:F2"/>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/alliance-templates/alliance-projects.xlsx
+++ b/docs/alliance-templates/alliance-projects.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="合作项目" sheetId="1" state="visible" r:id="rId1"/>
@@ -67,7 +67,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -90,11 +90,55 @@
         <color rgb="00B0B0B0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B0B0B0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B0B0B0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B0B0B0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -110,6 +154,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -470,11 +516,11 @@
 描述：文本，选填</t>
         </is>
       </c>
-      <c r="B1" s="4" t="n"/>
-      <c r="C1" s="4" t="n"/>
-      <c r="D1" s="4" t="n"/>
-      <c r="E1" s="4" t="n"/>
-      <c r="F1" s="4" t="n"/>
+      <c r="B1" s="7" t="n"/>
+      <c r="C1" s="7" t="n"/>
+      <c r="D1" s="7" t="n"/>
+      <c r="E1" s="7" t="n"/>
+      <c r="F1" s="8" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
@@ -521,7 +567,7 @@
       </c>
       <c r="C3" s="6" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>执行中</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
@@ -553,7 +599,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>执行中</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -585,7 +631,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>initiation</t>
+          <t>启动</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -617,7 +663,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>execution</t>
+          <t>执行中</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -649,7 +695,7 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>initiation</t>
+          <t>启动</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
